--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/PseudoAnnotated/log_results/noise_log_1024_0_5_0_7_test_0_12.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/PseudoAnnotated/log_results/noise_log_1024_0_5_0_7_test_0_12.xlsx
@@ -772,7 +772,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -839,17 +839,17 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -1190,7 +1190,7 @@
     <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>25</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>30</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>42</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>48</v>
       </c>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q7" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>56</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>60</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>66</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>71</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>75</v>
       </c>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Q13" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>78</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>82</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>88</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>91</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>92</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>97</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>101</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>102</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>106</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>110</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>114</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>115</v>
       </c>
